--- a/preguntas.xlsx
+++ b/preguntas.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preguntas'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preguntas'!$A$1:$J$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,10 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +485,26 @@
           <t>Respuesta</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Imagen pregunta</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Imagen respuesta</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Autora</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -509,6 +533,18 @@
           <t>Junio</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>ej-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -537,6 +573,18 @@
           <t>12 de octubre</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ej-02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -569,6 +617,18 @@
           <t>Marta</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ej-03</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -593,6 +653,18 @@
           <t>Ana, 7 minutos</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ej-04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -621,6 +693,18 @@
           <t>Cádiz</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ej-05</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -649,6 +733,18 @@
           <t>Un camarero desconocido</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>ej-06</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -673,6 +769,18 @@
           <t>Lucía</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>ej-07</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -697,6 +805,18 @@
           <t>Un mosto con hielo</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>ej-08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -721,6 +841,18 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ej-09</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -745,6 +877,18 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>ej-10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -773,6 +917,18 @@
           <t>Ana</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ej-11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -801,9 +957,21 @@
           <t>La lámpara del salón</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ej-12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:J13"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Normal,Difícil"</formula1>
@@ -819,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -878,10 +1046,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Imagen pregunta / Imagen respuesta: nombre del archivo de la foto dentro de la carpeta «imagenes» del proyecto (opcional).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Autora e ID: los rellena la web. Si añades filas a mano puedes dejarlos vacíos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Lo más fácil: crear las preguntas desde la web, en la pestaña «Crear preguntas».</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>No cambies el nombre del archivo (preguntas.xlsx) ni de la hoja. Añade tantas filas como quieras.</t>
         </is>

--- a/preguntas.xlsx
+++ b/preguntas.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preguntas'!$A$1:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preguntas'!$A$1:$J$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -970,8 +970,136 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Duelo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>El primer equipo que diga 5 bares a los que hayamos ido juntas</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Gana quien lo diga antes sin repetir</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ej-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Duelo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>¿En qué año nos conocimos todas? Gana quien se acerque más</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>ej-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Imitad a alguien del grupo sin decir su nombre: el resto adivina</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Gana el equipo que más acierte en 1 minuto</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ej-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Dibujad de memoria el logo del bar de siempre en 30 segundos</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>La mesa vota el mejor dibujo</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Lucía</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>ej-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J17"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Normal,Difícil"</formula1>
@@ -987,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1006,74 +1134,81 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Categoría: el nombre de la categoría. Usa siempre el mismo texto. Las 6 primeras categorías que aparezcan reciben los 6 colores del Trivial, en este orden: azul, rosa, verde, naranja, amarillo, rojo.</t>
+          <t>Categoría: el nombre de la categoría. Escribe «Duelo» o «Reto» para las casillas especiales (no cuentan como color).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Dificultad: «Normal» o «Difícil». Las difíciles salen cuando activas «Pregunta de quesito».</t>
+          <t>Categoría (colores): Usa siempre el mismo texto. Las 6 primeras categorías que aparezcan reciben los 6 colores del Trivial, en este orden: azul, rosa, verde, naranja, amarillo, rojo.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Persona: si esa persona está en el equipo que juega, la pregunta no le saldrá. Puedes poner varias separadas por comas.</t>
+          <t>Dificultad: «Normal» o «Difícil». Las difíciles salen cuando activas «Pregunta de quesito».</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Pregunta: el texto de la pregunta.</t>
+          <t>Persona: si esa persona está en el equipo que juega, la pregunta no le saldrá. Puedes poner varias separadas por comas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Opciones: déjalo vacío si es pregunta abierta. Si es tipo test, separa las opciones con punto y coma (;).</t>
+          <t>Pregunta: el texto de la pregunta.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Respuesta: la respuesta correcta. Se muestra al pulsar «Ver respuesta».</t>
+          <t>Opciones: déjalo vacío si es pregunta abierta. Si es tipo test, separa las opciones con punto y coma (;).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Imagen pregunta / Imagen respuesta: nombre del archivo de la foto dentro de la carpeta «imagenes» del proyecto (opcional).</t>
+          <t>Respuesta: la respuesta correcta. Se muestra al pulsar «Ver respuesta».</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Imagen pregunta / Imagen respuesta: nombre del archivo de la foto dentro de la carpeta «imagenes» del proyecto (opcional).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Autora e ID: los rellena la web. Si añades filas a mano puedes dejarlos vacíos.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Lo más fácil: crear las preguntas desde la web, en la pestaña «Crear preguntas».</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>No cambies el nombre del archivo (preguntas.xlsx) ni de la hoja. Añade tantas filas como quieras.</t>
         </is>
